--- a/RALENTI EXCESIVO.xlsx
+++ b/RALENTI EXCESIVO.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E51"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -420,53 +420,53 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>EN_0258 (taller chillan)</v>
+        <v>EN_0304 (MA9727 Curepto)</v>
       </c>
       <c r="B2">
-        <v>5340</v>
+        <v>5336</v>
       </c>
       <c r="C2" t="str">
-        <v>2026/07/22 23:02:18</v>
+        <v>2026/07/30 16:05:07</v>
       </c>
       <c r="D2" t="str">
-        <v>2026/07/23 04:50:41</v>
+        <v>2026/07/30 16:05:14</v>
       </c>
       <c r="E2" t="str">
-        <v>05:48:23</v>
+        <v>00:00:07</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>EN_0258 (taller chillan)</v>
+        <v>EN_0312 (SQM Antofagasta)</v>
       </c>
       <c r="B3">
-        <v>5340</v>
+        <v>5331</v>
       </c>
       <c r="C3" t="str">
-        <v>2026/07/24 14:40:11</v>
+        <v>2026/07/28 00:38:02</v>
       </c>
       <c r="D3" t="str">
-        <v>2026/07/24 14:40:18</v>
+        <v>2026/07/28 03:27:21</v>
       </c>
       <c r="E3" t="str">
-        <v>00:00:07</v>
+        <v>02:49:19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>EN_0304 (MA9727 Curepto)</v>
+        <v>EN_0356 (SQM Antofagasta)</v>
       </c>
       <c r="B4">
-        <v>5336</v>
+        <v>5296</v>
       </c>
       <c r="C4" t="str">
-        <v>2026/07/20 22:07:49</v>
+        <v>2026/07/27 22:32:25</v>
       </c>
       <c r="D4" t="str">
-        <v>2026/07/26 00:25:09</v>
+        <v>2026/07/28 13:26:17</v>
       </c>
       <c r="E4" t="str">
-        <v>122:17:20</v>
+        <v>14:53:52</v>
       </c>
     </row>
     <row r="5">
@@ -477,13 +477,13 @@
         <v>5296</v>
       </c>
       <c r="C5" t="str">
-        <v>2026/07/20 12:22:47</v>
+        <v>2026/07/28 14:38:27</v>
       </c>
       <c r="D5" t="str">
-        <v>2026/07/20 13:47:35</v>
+        <v>2026/07/28 14:48:09</v>
       </c>
       <c r="E5" t="str">
-        <v>01:24:48</v>
+        <v>00:09:42</v>
       </c>
     </row>
     <row r="6">
@@ -494,13 +494,13 @@
         <v>5296</v>
       </c>
       <c r="C6" t="str">
-        <v>2026/07/24 22:37:20</v>
+        <v>2026/07/28 18:34:33</v>
       </c>
       <c r="D6" t="str">
-        <v>2026/07/25 15:21:29</v>
+        <v>2026/07/28 19:41:14</v>
       </c>
       <c r="E6" t="str">
-        <v>16:44:09</v>
+        <v>01:06:41</v>
       </c>
     </row>
     <row r="7">
@@ -511,13 +511,13 @@
         <v>5296</v>
       </c>
       <c r="C7" t="str">
-        <v>2026/07/26 16:01:30</v>
+        <v>2026/07/30 17:16:27</v>
       </c>
       <c r="D7" t="str">
-        <v>2026/07/26 16:05:03</v>
+        <v>2026/07/30 17:17:58</v>
       </c>
       <c r="E7" t="str">
-        <v>00:03:33</v>
+        <v>00:01:31</v>
       </c>
     </row>
     <row r="8">
@@ -528,13 +528,13 @@
         <v>5296</v>
       </c>
       <c r="C8" t="str">
-        <v>2026/07/26 16:52:30</v>
+        <v>2026/07/30 17:49:05</v>
       </c>
       <c r="D8" t="str">
-        <v>2026/07/26 17:13:51</v>
+        <v>2026/07/30 17:54:07</v>
       </c>
       <c r="E8" t="str">
-        <v>00:21:21</v>
+        <v>00:05:02</v>
       </c>
     </row>
     <row r="9">
@@ -545,13 +545,13 @@
         <v>5296</v>
       </c>
       <c r="C9" t="str">
-        <v>2026/07/26 17:29:08</v>
+        <v>2026/07/30 18:07:30</v>
       </c>
       <c r="D9" t="str">
-        <v>2026/07/26 19:13:50</v>
+        <v>2026/07/30 18:09:58</v>
       </c>
       <c r="E9" t="str">
-        <v>01:44:42</v>
+        <v>00:02:28</v>
       </c>
     </row>
     <row r="10">
@@ -562,64 +562,64 @@
         <v>5296</v>
       </c>
       <c r="C10" t="str">
-        <v>2026/07/26 19:39:34</v>
+        <v>2026/08/01 21:18:37</v>
       </c>
       <c r="D10" t="str">
-        <v>2026/07/26 19:41:40</v>
+        <v>2026/08/01 21:38:18</v>
       </c>
       <c r="E10" t="str">
-        <v>00:02:06</v>
+        <v>00:19:41</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>EN_0356 (SQM Antofagasta)</v>
+        <v>MAXUS SRYB-26 (ANTOFA)</v>
       </c>
       <c r="B11">
-        <v>5296</v>
+        <v>3841</v>
       </c>
       <c r="C11" t="str">
-        <v>2026/07/26 20:14:09</v>
+        <v>2026/07/27 13:34:48</v>
       </c>
       <c r="D11" t="str">
-        <v>2026/07/26 20:15:14</v>
+        <v>2026/07/27 14:00:34</v>
       </c>
       <c r="E11" t="str">
-        <v>00:01:05</v>
+        <v>00:25:46</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>EN_0358 (SQM Antofagasta)</v>
+        <v>MAXUS SRYB-26 (ANTOFA)</v>
       </c>
       <c r="B12">
-        <v>5232</v>
+        <v>3841</v>
       </c>
       <c r="C12" t="str">
-        <v>2026/07/21 13:16:52</v>
+        <v>2026/07/27 14:39:09</v>
       </c>
       <c r="D12" t="str">
-        <v>2026/07/21 13:17:46</v>
+        <v>2026/07/27 15:56:16</v>
       </c>
       <c r="E12" t="str">
-        <v>00:00:54</v>
+        <v>01:17:07</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>EN_0358 (SQM Antofagasta)</v>
+        <v>MAXUS SRYB-26 (ANTOFA)</v>
       </c>
       <c r="B13">
-        <v>5232</v>
+        <v>3841</v>
       </c>
       <c r="C13" t="str">
-        <v>2026/07/21 13:27:57</v>
+        <v>2026/07/27 17:30:08</v>
       </c>
       <c r="D13" t="str">
-        <v>2026/07/21 15:28:55</v>
+        <v>2026/07/27 17:31:54</v>
       </c>
       <c r="E13" t="str">
-        <v>02:00:58</v>
+        <v>00:01:46</v>
       </c>
     </row>
     <row r="14">
@@ -630,13 +630,13 @@
         <v>3841</v>
       </c>
       <c r="C14" t="str">
-        <v>2026/07/20 15:11:56</v>
+        <v>2026/07/27 18:32:36</v>
       </c>
       <c r="D14" t="str">
-        <v>2026/07/20 15:55:44</v>
+        <v>2026/07/27 18:35:51</v>
       </c>
       <c r="E14" t="str">
-        <v>00:43:48</v>
+        <v>00:03:15</v>
       </c>
     </row>
     <row r="15">
@@ -647,13 +647,13 @@
         <v>3841</v>
       </c>
       <c r="C15" t="str">
-        <v>2026/07/20 16:12:13</v>
+        <v>2026/07/27 19:32:55</v>
       </c>
       <c r="D15" t="str">
-        <v>2026/07/20 16:16:05</v>
+        <v>2026/07/27 20:22:58</v>
       </c>
       <c r="E15" t="str">
-        <v>00:03:52</v>
+        <v>00:50:03</v>
       </c>
     </row>
     <row r="16">
@@ -664,13 +664,13 @@
         <v>3841</v>
       </c>
       <c r="C16" t="str">
-        <v>2026/07/20 19:14:51</v>
+        <v>2026/07/27 20:45:58</v>
       </c>
       <c r="D16" t="str">
-        <v>2026/07/20 19:33:41</v>
+        <v>2026/07/27 21:10:14</v>
       </c>
       <c r="E16" t="str">
-        <v>00:18:50</v>
+        <v>00:24:16</v>
       </c>
     </row>
     <row r="17">
@@ -681,13 +681,13 @@
         <v>3841</v>
       </c>
       <c r="C17" t="str">
-        <v>2026/07/20 19:53:51</v>
+        <v>2026/07/27 21:50:35</v>
       </c>
       <c r="D17" t="str">
-        <v>2026/07/20 20:40:29</v>
+        <v>2026/07/27 22:08:20</v>
       </c>
       <c r="E17" t="str">
-        <v>00:46:38</v>
+        <v>00:17:45</v>
       </c>
     </row>
     <row r="18">
@@ -698,13 +698,13 @@
         <v>3841</v>
       </c>
       <c r="C18" t="str">
-        <v>2026/07/20 21:11:12</v>
+        <v>2026/07/27 22:23:35</v>
       </c>
       <c r="D18" t="str">
-        <v>2026/07/20 21:19:12</v>
+        <v>2026/07/27 22:36:39</v>
       </c>
       <c r="E18" t="str">
-        <v>00:08:00</v>
+        <v>00:13:04</v>
       </c>
     </row>
     <row r="19">
@@ -715,13 +715,13 @@
         <v>3841</v>
       </c>
       <c r="C19" t="str">
-        <v>2026/07/21 14:52:35</v>
+        <v>2026/07/28 02:34:49</v>
       </c>
       <c r="D19" t="str">
-        <v>2026/07/21 14:54:38</v>
+        <v>2026/07/28 02:44:51</v>
       </c>
       <c r="E19" t="str">
-        <v>00:02:03</v>
+        <v>00:10:02</v>
       </c>
     </row>
     <row r="20">
@@ -732,13 +732,13 @@
         <v>3841</v>
       </c>
       <c r="C20" t="str">
-        <v>2026/07/21 15:30:35</v>
+        <v>2026/07/28 13:21:06</v>
       </c>
       <c r="D20" t="str">
-        <v>2026/07/21 15:40:36</v>
+        <v>2026/07/28 14:04:05</v>
       </c>
       <c r="E20" t="str">
-        <v>00:10:01</v>
+        <v>00:42:59</v>
       </c>
     </row>
     <row r="21">
@@ -749,13 +749,13 @@
         <v>3841</v>
       </c>
       <c r="C21" t="str">
-        <v>2026/07/21 15:56:50</v>
+        <v>2026/07/28 14:35:30</v>
       </c>
       <c r="D21" t="str">
-        <v>2026/07/21 16:45:48</v>
+        <v>2026/07/28 14:49:15</v>
       </c>
       <c r="E21" t="str">
-        <v>00:48:58</v>
+        <v>00:13:45</v>
       </c>
     </row>
     <row r="22">
@@ -766,13 +766,13 @@
         <v>3841</v>
       </c>
       <c r="C22" t="str">
-        <v>2026/07/21 16:56:54</v>
+        <v>2026/07/28 16:39:55</v>
       </c>
       <c r="D22" t="str">
-        <v>2026/07/21 16:59:06</v>
+        <v>2026/07/28 16:41:47</v>
       </c>
       <c r="E22" t="str">
-        <v>00:02:12</v>
+        <v>00:01:52</v>
       </c>
     </row>
     <row r="23">
@@ -783,13 +783,13 @@
         <v>3841</v>
       </c>
       <c r="C23" t="str">
-        <v>2026/07/21 17:35:49</v>
+        <v>2026/07/28 19:54:31</v>
       </c>
       <c r="D23" t="str">
-        <v>2026/07/21 17:39:29</v>
+        <v>2026/07/28 20:24:31</v>
       </c>
       <c r="E23" t="str">
-        <v>00:03:40</v>
+        <v>00:30:00</v>
       </c>
     </row>
     <row r="24">
@@ -800,13 +800,13 @@
         <v>3841</v>
       </c>
       <c r="C24" t="str">
-        <v>2026/07/21 17:53:35</v>
+        <v>2026/07/29 13:28:36</v>
       </c>
       <c r="D24" t="str">
-        <v>2026/07/21 17:59:53</v>
+        <v>2026/07/29 13:55:48</v>
       </c>
       <c r="E24" t="str">
-        <v>00:06:18</v>
+        <v>00:27:12</v>
       </c>
     </row>
     <row r="25">
@@ -817,13 +817,13 @@
         <v>3841</v>
       </c>
       <c r="C25" t="str">
-        <v>2026/07/21 18:58:30</v>
+        <v>2026/07/29 15:08:07</v>
       </c>
       <c r="D25" t="str">
-        <v>2026/07/21 19:00:28</v>
+        <v>2026/07/29 15:15:09</v>
       </c>
       <c r="E25" t="str">
-        <v>00:01:58</v>
+        <v>00:07:02</v>
       </c>
     </row>
     <row r="26">
@@ -834,13 +834,13 @@
         <v>3841</v>
       </c>
       <c r="C26" t="str">
-        <v>2026/07/21 19:37:30</v>
+        <v>2026/07/29 16:42:48</v>
       </c>
       <c r="D26" t="str">
-        <v>2026/07/21 19:55:40</v>
+        <v>2026/07/29 17:12:15</v>
       </c>
       <c r="E26" t="str">
-        <v>00:18:10</v>
+        <v>00:29:27</v>
       </c>
     </row>
     <row r="27">
@@ -851,13 +851,13 @@
         <v>3841</v>
       </c>
       <c r="C27" t="str">
-        <v>2026/07/21 20:10:16</v>
+        <v>2026/07/29 17:39:15</v>
       </c>
       <c r="D27" t="str">
-        <v>2026/07/21 20:28:52</v>
+        <v>2026/07/29 17:45:25</v>
       </c>
       <c r="E27" t="str">
-        <v>00:18:36</v>
+        <v>00:06:10</v>
       </c>
     </row>
     <row r="28">
@@ -868,13 +868,13 @@
         <v>3841</v>
       </c>
       <c r="C28" t="str">
-        <v>2026/07/21 20:39:59</v>
+        <v>2026/07/29 18:53:31</v>
       </c>
       <c r="D28" t="str">
-        <v>2026/07/21 20:43:01</v>
+        <v>2026/07/29 19:58:45</v>
       </c>
       <c r="E28" t="str">
-        <v>00:03:02</v>
+        <v>01:05:14</v>
       </c>
     </row>
     <row r="29">
@@ -885,13 +885,13 @@
         <v>3841</v>
       </c>
       <c r="C29" t="str">
-        <v>2026/07/22 13:35:38</v>
+        <v>2026/07/30 13:01:09</v>
       </c>
       <c r="D29" t="str">
-        <v>2026/07/22 14:27:42</v>
+        <v>2026/07/30 13:08:44</v>
       </c>
       <c r="E29" t="str">
-        <v>00:52:04</v>
+        <v>00:07:35</v>
       </c>
     </row>
     <row r="30">
@@ -902,13 +902,13 @@
         <v>3841</v>
       </c>
       <c r="C30" t="str">
-        <v>2026/07/22 15:08:48</v>
+        <v>2026/07/30 20:16:41</v>
       </c>
       <c r="D30" t="str">
-        <v>2026/07/22 15:24:41</v>
+        <v>2026/07/30 20:51:01</v>
       </c>
       <c r="E30" t="str">
-        <v>00:15:53</v>
+        <v>00:34:20</v>
       </c>
     </row>
     <row r="31">
@@ -919,13 +919,13 @@
         <v>3841</v>
       </c>
       <c r="C31" t="str">
-        <v>2026/07/22 16:31:38</v>
+        <v>2026/07/31 18:04:58</v>
       </c>
       <c r="D31" t="str">
-        <v>2026/07/22 16:41:20</v>
+        <v>2026/07/31 19:59:09</v>
       </c>
       <c r="E31" t="str">
-        <v>00:09:42</v>
+        <v>01:54:11</v>
       </c>
     </row>
     <row r="32">
@@ -936,13 +936,13 @@
         <v>3841</v>
       </c>
       <c r="C32" t="str">
-        <v>2026/07/22 16:54:30</v>
+        <v>2026/08/01 04:47:28</v>
       </c>
       <c r="D32" t="str">
-        <v>2026/07/22 17:06:02</v>
+        <v>2026/08/01 04:54:37</v>
       </c>
       <c r="E32" t="str">
-        <v>00:11:32</v>
+        <v>00:07:09</v>
       </c>
     </row>
     <row r="33">
@@ -953,501 +953,331 @@
         <v>3841</v>
       </c>
       <c r="C33" t="str">
-        <v>2026/07/22 18:28:09</v>
+        <v>2026/08/02 17:18:31</v>
       </c>
       <c r="D33" t="str">
-        <v>2026/07/22 18:36:40</v>
+        <v>2026/08/02 17:19:53</v>
       </c>
       <c r="E33" t="str">
-        <v>00:08:31</v>
+        <v>00:01:22</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>MAXUS SRYB-26 (ANTOFA)</v>
+        <v>MAXUS TVVB-25 (CHILLAN)</v>
       </c>
       <c r="B34">
-        <v>3841</v>
+        <v>4936</v>
       </c>
       <c r="C34" t="str">
-        <v>2026/07/22 19:15:59</v>
+        <v>2026/07/31 21:15:59</v>
       </c>
       <c r="D34" t="str">
-        <v>2026/07/22 19:50:24</v>
+        <v>2026/07/31 22:11:48</v>
       </c>
       <c r="E34" t="str">
-        <v>00:34:25</v>
+        <v>00:55:49</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>MAXUS SRYB-26 (ANTOFA)</v>
+        <v>MAXUS TVVB-25 (CHILLAN)</v>
       </c>
       <c r="B35">
-        <v>3841</v>
+        <v>4936</v>
       </c>
       <c r="C35" t="str">
-        <v>2026/07/22 20:04:01</v>
+        <v>2026/07/31 23:34:38</v>
       </c>
       <c r="D35" t="str">
-        <v>2026/07/22 20:19:11</v>
+        <v>2026/07/31 23:37:30</v>
       </c>
       <c r="E35" t="str">
-        <v>00:15:10</v>
+        <v>00:02:52</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>MAXUS SRYB-26 (ANTOFA)</v>
+        <v>MAXUS TYTC-88 (ANTOFA)</v>
       </c>
       <c r="B36">
-        <v>3841</v>
+        <v>3860</v>
       </c>
       <c r="C36" t="str">
-        <v>2026/07/22 20:30:55</v>
+        <v>2026/07/29 14:19:49</v>
       </c>
       <c r="D36" t="str">
-        <v>2026/07/22 20:43:07</v>
+        <v>2026/07/29 14:20:58</v>
       </c>
       <c r="E36" t="str">
-        <v>00:12:12</v>
+        <v>00:01:09</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>MAXUS SRYB-26 (ANTOFA)</v>
+        <v>MAXUS TYTC-88 (ANTOFA)</v>
       </c>
       <c r="B37">
-        <v>3841</v>
+        <v>3860</v>
       </c>
       <c r="C37" t="str">
-        <v>2026/07/22 21:11:52</v>
+        <v>2026/07/30 19:44:10</v>
       </c>
       <c r="D37" t="str">
-        <v>2026/07/22 21:18:32</v>
+        <v>2026/07/30 19:57:33</v>
       </c>
       <c r="E37" t="str">
-        <v>00:06:40</v>
+        <v>00:13:23</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>MAXUS SRYB-26 (ANTOFA)</v>
+        <v>MAXUS TYTC-88 (ANTOFA)</v>
       </c>
       <c r="B38">
-        <v>3841</v>
+        <v>3860</v>
       </c>
       <c r="C38" t="str">
-        <v>2026/07/23 15:26:52</v>
+        <v>2026/07/30 20:16:18</v>
       </c>
       <c r="D38" t="str">
-        <v>2026/07/23 15:29:12</v>
+        <v>2026/07/30 20:29:00</v>
       </c>
       <c r="E38" t="str">
-        <v>00:02:20</v>
+        <v>00:12:42</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>MAXUS SRYB-26 (ANTOFA)</v>
+        <v>MAXUS TYTC-88 (ANTOFA)</v>
       </c>
       <c r="B39">
-        <v>3841</v>
+        <v>3860</v>
       </c>
       <c r="C39" t="str">
-        <v>2026/07/23 16:06:04</v>
+        <v>2026/07/31 17:47:49</v>
       </c>
       <c r="D39" t="str">
-        <v>2026/07/23 16:08:47</v>
+        <v>2026/07/31 19:42:43</v>
       </c>
       <c r="E39" t="str">
-        <v>00:02:43</v>
+        <v>01:54:54</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>MAXUS SRYB-26 (ANTOFA)</v>
+        <v>MAXUS VGVV-89 (STGO)</v>
       </c>
       <c r="B40">
-        <v>3841</v>
+        <v>5633</v>
       </c>
       <c r="C40" t="str">
-        <v>2026/07/23 17:41:23</v>
+        <v>2026/07/29 13:57:54</v>
       </c>
       <c r="D40" t="str">
-        <v>2026/07/23 18:05:26</v>
+        <v>2026/07/29 16:12:06</v>
       </c>
       <c r="E40" t="str">
-        <v>00:24:03</v>
+        <v>02:14:12</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>MAXUS SRYB-26 (ANTOFA)</v>
+        <v>MAXUS VGVV-89 (STGO)</v>
       </c>
       <c r="B41">
-        <v>3841</v>
+        <v>5633</v>
       </c>
       <c r="C41" t="str">
-        <v>2026/07/23 20:14:41</v>
+        <v>2026/07/30 14:07:47</v>
       </c>
       <c r="D41" t="str">
-        <v>2026/07/23 20:29:37</v>
+        <v>2026/07/30 14:16:07</v>
       </c>
       <c r="E41" t="str">
-        <v>00:14:56</v>
+        <v>00:08:20</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>MAXUS SRYB-26 (ANTOFA)</v>
+        <v>MAXUS VGVV-89 (STGO)</v>
       </c>
       <c r="B42">
-        <v>3841</v>
+        <v>5633</v>
       </c>
       <c r="C42" t="str">
-        <v>2026/07/23 21:25:37</v>
+        <v>2026/07/30 14:26:37</v>
       </c>
       <c r="D42" t="str">
-        <v>2026/07/23 22:29:49</v>
+        <v>2026/07/30 14:38:59</v>
       </c>
       <c r="E42" t="str">
-        <v>01:04:12</v>
+        <v>00:12:22</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>MAXUS SRYB-26 (ANTOFA)</v>
+        <v>MAXUS VGVV-89 (STGO)</v>
       </c>
       <c r="B43">
-        <v>3841</v>
+        <v>5633</v>
       </c>
       <c r="C43" t="str">
-        <v>2026/07/24 15:43:44</v>
+        <v>2026/07/30 14:51:32</v>
       </c>
       <c r="D43" t="str">
-        <v>2026/07/24 15:56:36</v>
+        <v>2026/07/30 15:03:31</v>
       </c>
       <c r="E43" t="str">
-        <v>00:12:52</v>
+        <v>00:11:59</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>MAXUS SRYB-26 (ANTOFA)</v>
+        <v>MAXUS VGVV-89 (STGO)</v>
       </c>
       <c r="B44">
-        <v>3841</v>
+        <v>5633</v>
       </c>
       <c r="C44" t="str">
-        <v>2026/07/24 17:58:10</v>
+        <v>2026/07/30 15:26:05</v>
       </c>
       <c r="D44" t="str">
-        <v>2026/07/24 18:08:14</v>
+        <v>2026/07/30 15:46:27</v>
       </c>
       <c r="E44" t="str">
-        <v>00:10:04</v>
+        <v>00:20:22</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>MAXUS SRYB-26 (ANTOFA)</v>
+        <v>MAXUS VGVV-89 (STGO)</v>
       </c>
       <c r="B45">
-        <v>3841</v>
+        <v>5633</v>
       </c>
       <c r="C45" t="str">
-        <v>2026/07/24 18:55:40</v>
+        <v>2026/07/30 16:47:03</v>
       </c>
       <c r="D45" t="str">
-        <v>2026/07/24 19:10:38</v>
+        <v>2026/07/30 16:48:52</v>
       </c>
       <c r="E45" t="str">
-        <v>00:14:58</v>
+        <v>00:01:49</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>MAXUS SRYB-26 (ANTOFA)</v>
+        <v>MITSUBISHI VDYY-73 (Chillan)</v>
       </c>
       <c r="B46">
-        <v>3841</v>
+        <v>5220</v>
       </c>
       <c r="C46" t="str">
-        <v>2026/07/24 19:40:09</v>
+        <v>2026/07/27 15:46:14</v>
       </c>
       <c r="D46" t="str">
-        <v>2026/07/24 20:00:49</v>
+        <v>2026/07/27 15:50:31</v>
       </c>
       <c r="E46" t="str">
-        <v>00:20:40</v>
+        <v>00:04:17</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>MAXUS SRYB-26 (ANTOFA)</v>
+        <v>MITSUBISHI VDYY-73 (Chillan)</v>
       </c>
       <c r="B47">
-        <v>3841</v>
+        <v>5220</v>
       </c>
       <c r="C47" t="str">
-        <v>2026/07/25 12:04:17</v>
+        <v>2026/07/28 20:58:54</v>
       </c>
       <c r="D47" t="str">
-        <v>2026/07/25 13:35:32</v>
+        <v>2026/07/28 21:16:43</v>
       </c>
       <c r="E47" t="str">
-        <v>01:31:15</v>
+        <v>00:17:49</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>MAXUS SSRZ-79 (VENTAS Copiapo)</v>
+        <v>MITSUBISHI VDYY-82 (ANTOFA)</v>
       </c>
       <c r="B48">
-        <v>5204</v>
+        <v>5635</v>
       </c>
       <c r="C48" t="str">
-        <v>2026/07/20 13:07:00</v>
+        <v>2026/07/28 06:28:24</v>
       </c>
       <c r="D48" t="str">
-        <v>2026/07/20 13:23:27</v>
+        <v>2026/07/28 06:41:26</v>
       </c>
       <c r="E48" t="str">
-        <v>00:16:27</v>
+        <v>00:13:02</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>MAXUS TVVB-25 (CHILLAN)</v>
+        <v>PEUGEOT SVCH-53 (STGO)</v>
       </c>
       <c r="B49">
-        <v>4936</v>
+        <v>5223</v>
       </c>
       <c r="C49" t="str">
-        <v>2026/07/20 12:55:38</v>
+        <v>2026/07/30 15:03:49</v>
       </c>
       <c r="D49" t="str">
-        <v>2026/07/20 12:58:49</v>
+        <v>2026/07/30 15:09:51</v>
       </c>
       <c r="E49" t="str">
-        <v>00:03:11</v>
+        <v>00:06:02</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>MAXUS TVVB-25 (CHILLAN)</v>
+        <v>PEUGEOT SVCH-53 (STGO)</v>
       </c>
       <c r="B50">
-        <v>4936</v>
+        <v>5223</v>
       </c>
       <c r="C50" t="str">
-        <v>2026/07/23 13:20:25</v>
+        <v>2026/07/30 15:25:24</v>
       </c>
       <c r="D50" t="str">
-        <v>2026/07/23 15:07:03</v>
+        <v>2026/07/30 15:55:12</v>
       </c>
       <c r="E50" t="str">
-        <v>01:46:38</v>
+        <v>00:29:48</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>MAXUS TVVB-25 (CHILLAN)</v>
+        <v>PEUGEOT SVCH-53 (STGO)</v>
       </c>
       <c r="B51">
-        <v>4936</v>
+        <v>5223</v>
       </c>
       <c r="C51" t="str">
-        <v>2026/07/23 15:27:43</v>
+        <v>2026/07/30 19:35:42</v>
       </c>
       <c r="D51" t="str">
-        <v>2026/07/23 15:31:10</v>
+        <v>2026/07/30 19:41:13</v>
       </c>
       <c r="E51" t="str">
-        <v>00:03:27</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="str">
-        <v>MAXUS TVVB-25 (CHILLAN)</v>
-      </c>
-      <c r="B52">
-        <v>4936</v>
-      </c>
-      <c r="C52" t="str">
-        <v>2026/07/23 16:04:30</v>
-      </c>
-      <c r="D52" t="str">
-        <v>2026/07/23 16:07:49</v>
-      </c>
-      <c r="E52" t="str">
-        <v>00:03:19</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="str">
-        <v>MAXUS TVVB-25 (CHILLAN)</v>
-      </c>
-      <c r="B53">
-        <v>4936</v>
-      </c>
-      <c r="C53" t="str">
-        <v>2026/07/23 19:42:36</v>
-      </c>
-      <c r="D53" t="str">
-        <v>2026/07/23 19:43:48</v>
-      </c>
-      <c r="E53" t="str">
-        <v>00:01:12</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="str">
-        <v>MAXUS TVVB-25 (CHILLAN)</v>
-      </c>
-      <c r="B54">
-        <v>4936</v>
-      </c>
-      <c r="C54" t="str">
-        <v>2026/07/24 14:50:11</v>
-      </c>
-      <c r="D54" t="str">
-        <v>2026/07/24 14:58:34</v>
-      </c>
-      <c r="E54" t="str">
-        <v>00:08:23</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="str">
-        <v>MAXUS TYTC-88 (ANTOFA)</v>
-      </c>
-      <c r="B55">
-        <v>3860</v>
-      </c>
-      <c r="C55" t="str">
-        <v>2026/07/20 14:10:48</v>
-      </c>
-      <c r="D55" t="str">
-        <v>2026/07/20 14:25:36</v>
-      </c>
-      <c r="E55" t="str">
-        <v>00:14:48</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="str">
-        <v>MAXUS TYTC-88 (ANTOFA)</v>
-      </c>
-      <c r="B56">
-        <v>3860</v>
-      </c>
-      <c r="C56" t="str">
-        <v>2026/07/22 16:36:48</v>
-      </c>
-      <c r="D56" t="str">
-        <v>2026/07/22 16:45:00</v>
-      </c>
-      <c r="E56" t="str">
-        <v>00:08:12</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="str">
-        <v>MITSUBISHI VDYY-73 (Chillan)</v>
-      </c>
-      <c r="B57">
-        <v>5220</v>
-      </c>
-      <c r="C57" t="str">
-        <v>2026/07/22 19:32:11</v>
-      </c>
-      <c r="D57" t="str">
-        <v>2026/07/22 19:40:31</v>
-      </c>
-      <c r="E57" t="str">
-        <v>00:08:20</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="str">
-        <v>MITSUBISHI VDYY-73 (Chillan)</v>
-      </c>
-      <c r="B58">
-        <v>5220</v>
-      </c>
-      <c r="C58" t="str">
-        <v>2026/07/25 18:54:40</v>
-      </c>
-      <c r="D58" t="str">
-        <v>2026/07/25 18:56:49</v>
-      </c>
-      <c r="E58" t="str">
-        <v>00:02:09</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="str">
-        <v>MITSUBISHI VDYY-82 (ANTOFA)</v>
-      </c>
-      <c r="B59">
-        <v>5635</v>
-      </c>
-      <c r="C59" t="str">
-        <v>2026/07/23 09:39:32</v>
-      </c>
-      <c r="D59" t="str">
-        <v>2026/07/23 09:48:45</v>
-      </c>
-      <c r="E59" t="str">
-        <v>00:09:13</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="str">
-        <v>MITSUBISHI VDYY-82 (ANTOFA)</v>
-      </c>
-      <c r="B60">
-        <v>5635</v>
-      </c>
-      <c r="C60" t="str">
-        <v>2026/07/24 11:49:41</v>
-      </c>
-      <c r="D60" t="str">
-        <v>2026/07/24 11:51:58</v>
-      </c>
-      <c r="E60" t="str">
-        <v>00:02:17</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="str">
-        <v>PEUGEOT SVCH-53 (STGO)</v>
-      </c>
-      <c r="B61">
-        <v>5223</v>
-      </c>
-      <c r="C61" t="str">
-        <v>2026/07/23 13:30:18</v>
-      </c>
-      <c r="D61" t="str">
-        <v>2026/07/23 13:32:18</v>
-      </c>
-      <c r="E61" t="str">
-        <v>00:02:00</v>
+        <v>00:05:31</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E61"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E51"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D24"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1465,44 +1295,44 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>EN_0258 (taller chillan)</v>
+        <v>EN_0304 (MA9727 Curepto)</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-07-22</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="str">
-        <v>05:48:23</v>
+        <v>00:00:07</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>EN_0258 (taller chillan)</v>
+        <v>EN_0312 (SQM Antofagasta)</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-07-24</v>
+        <v>2026-07-28</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3" t="str">
-        <v>00:00:07</v>
+        <v>02:49:19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>EN_0304 (MA9727 Curepto)</v>
+        <v>EN_0356 (SQM Antofagasta)</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-07-20</v>
+        <v>2026-07-27</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="str">
-        <v>122:17:20</v>
+        <v>14:53:52</v>
       </c>
     </row>
     <row r="5">
@@ -1510,13 +1340,13 @@
         <v>EN_0356 (SQM Antofagasta)</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-07-20</v>
+        <v>2026-07-28</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="str">
-        <v>01:24:48</v>
+        <v>01:16:23</v>
       </c>
     </row>
     <row r="6">
@@ -1524,13 +1354,13 @@
         <v>EN_0356 (SQM Antofagasta)</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-07-24</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D6" t="str">
-        <v>16:44:09</v>
+        <v>00:09:01</v>
       </c>
     </row>
     <row r="7">
@@ -1538,27 +1368,27 @@
         <v>EN_0356 (SQM Antofagasta)</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-07-26</v>
+        <v>2026-08-01</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D7" t="str">
-        <v>02:12:47</v>
+        <v>00:19:41</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>EN_0358 (SQM Antofagasta)</v>
+        <v>MAXUS SRYB-26 (ANTOFA)</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-07-21</v>
+        <v>2026-07-27</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D8" t="str">
-        <v>02:01:52</v>
+        <v>03:33:02</v>
       </c>
     </row>
     <row r="9">
@@ -1566,13 +1396,13 @@
         <v>MAXUS SRYB-26 (ANTOFA)</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-07-20</v>
+        <v>2026-07-28</v>
       </c>
       <c r="C9">
         <v>5</v>
       </c>
       <c r="D9" t="str">
-        <v>02:01:08</v>
+        <v>01:38:38</v>
       </c>
     </row>
     <row r="10">
@@ -1580,13 +1410,13 @@
         <v>MAXUS SRYB-26 (ANTOFA)</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-07-21</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C10">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D10" t="str">
-        <v>01:54:58</v>
+        <v>02:15:05</v>
       </c>
     </row>
     <row r="11">
@@ -1594,13 +1424,13 @@
         <v>MAXUS SRYB-26 (ANTOFA)</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-07-22</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C11">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D11" t="str">
-        <v>02:46:09</v>
+        <v>00:41:55</v>
       </c>
     </row>
     <row r="12">
@@ -1608,13 +1438,13 @@
         <v>MAXUS SRYB-26 (ANTOFA)</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-07-23</v>
+        <v>2026-07-31</v>
       </c>
       <c r="C12">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D12" t="str">
-        <v>01:48:14</v>
+        <v>01:54:11</v>
       </c>
     </row>
     <row r="13">
@@ -1622,13 +1452,13 @@
         <v>MAXUS SRYB-26 (ANTOFA)</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-07-24</v>
+        <v>2026-08-01</v>
       </c>
       <c r="C13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D13" t="str">
-        <v>00:58:34</v>
+        <v>00:07:09</v>
       </c>
     </row>
     <row r="14">
@@ -1636,97 +1466,97 @@
         <v>MAXUS SRYB-26 (ANTOFA)</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-07-25</v>
+        <v>2026-08-02</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14" t="str">
-        <v>01:31:15</v>
+        <v>00:01:22</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>MAXUS SSRZ-79 (VENTAS Copiapo)</v>
+        <v>MAXUS TVVB-25 (CHILLAN)</v>
       </c>
       <c r="B15" t="str">
-        <v>2026-07-20</v>
+        <v>2026-07-31</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="str">
-        <v>00:16:27</v>
+        <v>00:58:41</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>MAXUS TVVB-25 (CHILLAN)</v>
+        <v>MAXUS TYTC-88 (ANTOFA)</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-07-20</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="D16" t="str">
-        <v>00:03:11</v>
+        <v>00:01:09</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>MAXUS TVVB-25 (CHILLAN)</v>
+        <v>MAXUS TYTC-88 (ANTOFA)</v>
       </c>
       <c r="B17" t="str">
-        <v>2026-07-23</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C17">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D17" t="str">
-        <v>01:54:36</v>
+        <v>00:26:05</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>MAXUS TVVB-25 (CHILLAN)</v>
+        <v>MAXUS TYTC-88 (ANTOFA)</v>
       </c>
       <c r="B18" t="str">
-        <v>2026-07-24</v>
+        <v>2026-07-31</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
       <c r="D18" t="str">
-        <v>00:08:23</v>
+        <v>01:54:54</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>MAXUS TYTC-88 (ANTOFA)</v>
+        <v>MAXUS VGVV-89 (STGO)</v>
       </c>
       <c r="B19" t="str">
-        <v>2026-07-20</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C19">
         <v>1</v>
       </c>
       <c r="D19" t="str">
-        <v>00:14:48</v>
+        <v>02:14:12</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>MAXUS TYTC-88 (ANTOFA)</v>
+        <v>MAXUS VGVV-89 (STGO)</v>
       </c>
       <c r="B20" t="str">
-        <v>2026-07-22</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D20" t="str">
-        <v>00:08:12</v>
+        <v>00:54:52</v>
       </c>
     </row>
     <row r="21">
@@ -1734,13 +1564,13 @@
         <v>MITSUBISHI VDYY-73 (Chillan)</v>
       </c>
       <c r="B21" t="str">
-        <v>2026-07-22</v>
+        <v>2026-07-27</v>
       </c>
       <c r="C21">
         <v>1</v>
       </c>
       <c r="D21" t="str">
-        <v>00:08:20</v>
+        <v>00:04:17</v>
       </c>
     </row>
     <row r="22">
@@ -1748,13 +1578,13 @@
         <v>MITSUBISHI VDYY-73 (Chillan)</v>
       </c>
       <c r="B22" t="str">
-        <v>2026-07-25</v>
+        <v>2026-07-28</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22" t="str">
-        <v>00:02:09</v>
+        <v>00:17:49</v>
       </c>
     </row>
     <row r="23">
@@ -1762,53 +1592,39 @@
         <v>MITSUBISHI VDYY-82 (ANTOFA)</v>
       </c>
       <c r="B23" t="str">
-        <v>2026-07-23</v>
+        <v>2026-07-28</v>
       </c>
       <c r="C23">
         <v>1</v>
       </c>
       <c r="D23" t="str">
-        <v>00:09:13</v>
+        <v>00:13:02</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>MITSUBISHI VDYY-82 (ANTOFA)</v>
+        <v>PEUGEOT SVCH-53 (STGO)</v>
       </c>
       <c r="B24" t="str">
-        <v>2026-07-24</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D24" t="str">
-        <v>00:02:17</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>PEUGEOT SVCH-53 (STGO)</v>
-      </c>
-      <c r="B25" t="str">
-        <v>2026-07-23</v>
-      </c>
-      <c r="C25">
-        <v>1</v>
-      </c>
-      <c r="D25" t="str">
-        <v>00:02:00</v>
+        <v>00:41:21</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D25"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D24"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1823,24 +1639,24 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>EN_0258 (taller chillan)</v>
+        <v>EN_0304 (MA9727 Curepto)</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>05:48:30</v>
+        <v>00:00:07</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>EN_0304 (MA9727 Curepto)</v>
+        <v>EN_0312 (SQM Antofagasta)</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="str">
-        <v>122:17:20</v>
+        <v>02:49:19</v>
       </c>
     </row>
     <row r="4">
@@ -1851,100 +1667,89 @@
         <v>7</v>
       </c>
       <c r="C4" t="str">
-        <v>20:21:44</v>
+        <v>16:38:57</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>EN_0358 (SQM Antofagasta)</v>
+        <v>MAXUS SRYB-26 (ANTOFA)</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="C5" t="str">
-        <v>02:01:52</v>
+        <v>10:11:22</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>MAXUS SRYB-26 (ANTOFA)</v>
+        <v>MAXUS TVVB-25 (CHILLAN)</v>
       </c>
       <c r="B6">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="C6" t="str">
-        <v>11:00:18</v>
+        <v>00:58:41</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>MAXUS SSRZ-79 (VENTAS Copiapo)</v>
+        <v>MAXUS TYTC-88 (ANTOFA)</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C7" t="str">
-        <v>00:16:27</v>
+        <v>02:22:08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>MAXUS TVVB-25 (CHILLAN)</v>
+        <v>MAXUS VGVV-89 (STGO)</v>
       </c>
       <c r="B8">
         <v>6</v>
       </c>
       <c r="C8" t="str">
-        <v>02:06:10</v>
+        <v>03:09:04</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>MAXUS TYTC-88 (ANTOFA)</v>
+        <v>MITSUBISHI VDYY-73 (Chillan)</v>
       </c>
       <c r="B9">
         <v>2</v>
       </c>
       <c r="C9" t="str">
-        <v>00:23:00</v>
+        <v>00:22:06</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>MITSUBISHI VDYY-73 (Chillan)</v>
+        <v>MITSUBISHI VDYY-82 (ANTOFA)</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" t="str">
-        <v>00:10:29</v>
+        <v>00:13:02</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>MITSUBISHI VDYY-82 (ANTOFA)</v>
+        <v>PEUGEOT SVCH-53 (STGO)</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="str">
-        <v>00:11:30</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>PEUGEOT SVCH-53 (STGO)</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12" t="str">
-        <v>00:02:00</v>
+        <v>00:41:21</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/RALENTI EXCESIVO.xlsx
+++ b/RALENTI EXCESIVO.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E42"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -420,155 +420,155 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>EN_0304 (MA9727 Curepto)</v>
+        <v>MAXUS SRYB-26 (ANTOFA)</v>
       </c>
       <c r="B2">
-        <v>5336</v>
+        <v>3841</v>
       </c>
       <c r="C2" t="str">
-        <v>2026/07/30 16:05:07</v>
+        <v>2026/07/27 13:34:48</v>
       </c>
       <c r="D2" t="str">
-        <v>2026/07/30 16:05:14</v>
+        <v>2026/07/27 14:00:34</v>
       </c>
       <c r="E2" t="str">
-        <v>00:00:07</v>
+        <v>00:25:46</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>EN_0312 (SQM Antofagasta)</v>
+        <v>MAXUS SRYB-26 (ANTOFA)</v>
       </c>
       <c r="B3">
-        <v>5331</v>
+        <v>3841</v>
       </c>
       <c r="C3" t="str">
-        <v>2026/07/28 00:38:02</v>
+        <v>2026/07/27 14:39:09</v>
       </c>
       <c r="D3" t="str">
-        <v>2026/07/28 03:27:21</v>
+        <v>2026/07/27 15:56:16</v>
       </c>
       <c r="E3" t="str">
-        <v>02:49:19</v>
+        <v>01:17:07</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>EN_0356 (SQM Antofagasta)</v>
+        <v>MAXUS SRYB-26 (ANTOFA)</v>
       </c>
       <c r="B4">
-        <v>5296</v>
+        <v>3841</v>
       </c>
       <c r="C4" t="str">
-        <v>2026/07/27 22:32:25</v>
+        <v>2026/07/27 17:30:08</v>
       </c>
       <c r="D4" t="str">
-        <v>2026/07/28 13:26:17</v>
+        <v>2026/07/27 17:31:54</v>
       </c>
       <c r="E4" t="str">
-        <v>14:53:52</v>
+        <v>00:01:46</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>EN_0356 (SQM Antofagasta)</v>
+        <v>MAXUS SRYB-26 (ANTOFA)</v>
       </c>
       <c r="B5">
-        <v>5296</v>
+        <v>3841</v>
       </c>
       <c r="C5" t="str">
-        <v>2026/07/28 14:38:27</v>
+        <v>2026/07/27 18:32:36</v>
       </c>
       <c r="D5" t="str">
-        <v>2026/07/28 14:48:09</v>
+        <v>2026/07/27 18:35:51</v>
       </c>
       <c r="E5" t="str">
-        <v>00:09:42</v>
+        <v>00:03:15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>EN_0356 (SQM Antofagasta)</v>
+        <v>MAXUS SRYB-26 (ANTOFA)</v>
       </c>
       <c r="B6">
-        <v>5296</v>
+        <v>3841</v>
       </c>
       <c r="C6" t="str">
-        <v>2026/07/28 18:34:33</v>
+        <v>2026/07/27 19:32:55</v>
       </c>
       <c r="D6" t="str">
-        <v>2026/07/28 19:41:14</v>
+        <v>2026/07/27 20:22:58</v>
       </c>
       <c r="E6" t="str">
-        <v>01:06:41</v>
+        <v>00:50:03</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>EN_0356 (SQM Antofagasta)</v>
+        <v>MAXUS SRYB-26 (ANTOFA)</v>
       </c>
       <c r="B7">
-        <v>5296</v>
+        <v>3841</v>
       </c>
       <c r="C7" t="str">
-        <v>2026/07/30 17:16:27</v>
+        <v>2026/07/27 20:45:58</v>
       </c>
       <c r="D7" t="str">
-        <v>2026/07/30 17:17:58</v>
+        <v>2026/07/27 21:10:14</v>
       </c>
       <c r="E7" t="str">
-        <v>00:01:31</v>
+        <v>00:24:16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>EN_0356 (SQM Antofagasta)</v>
+        <v>MAXUS SRYB-26 (ANTOFA)</v>
       </c>
       <c r="B8">
-        <v>5296</v>
+        <v>3841</v>
       </c>
       <c r="C8" t="str">
-        <v>2026/07/30 17:49:05</v>
+        <v>2026/07/27 21:50:35</v>
       </c>
       <c r="D8" t="str">
-        <v>2026/07/30 17:54:07</v>
+        <v>2026/07/27 22:08:20</v>
       </c>
       <c r="E8" t="str">
-        <v>00:05:02</v>
+        <v>00:17:45</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>EN_0356 (SQM Antofagasta)</v>
+        <v>MAXUS SRYB-26 (ANTOFA)</v>
       </c>
       <c r="B9">
-        <v>5296</v>
+        <v>3841</v>
       </c>
       <c r="C9" t="str">
-        <v>2026/07/30 18:07:30</v>
+        <v>2026/07/27 22:23:35</v>
       </c>
       <c r="D9" t="str">
-        <v>2026/07/30 18:09:58</v>
+        <v>2026/07/27 22:36:39</v>
       </c>
       <c r="E9" t="str">
-        <v>00:02:28</v>
+        <v>00:13:04</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>EN_0356 (SQM Antofagasta)</v>
+        <v>MAXUS SRYB-26 (ANTOFA)</v>
       </c>
       <c r="B10">
-        <v>5296</v>
+        <v>3841</v>
       </c>
       <c r="C10" t="str">
-        <v>2026/08/01 21:18:37</v>
+        <v>2026/07/28 02:34:49</v>
       </c>
       <c r="D10" t="str">
-        <v>2026/08/01 21:38:18</v>
+        <v>2026/07/28 02:44:51</v>
       </c>
       <c r="E10" t="str">
-        <v>00:19:41</v>
+        <v>00:10:02</v>
       </c>
     </row>
     <row r="11">
@@ -579,13 +579,13 @@
         <v>3841</v>
       </c>
       <c r="C11" t="str">
-        <v>2026/07/27 13:34:48</v>
+        <v>2026/07/28 13:21:06</v>
       </c>
       <c r="D11" t="str">
-        <v>2026/07/27 14:00:34</v>
+        <v>2026/07/28 14:04:05</v>
       </c>
       <c r="E11" t="str">
-        <v>00:25:46</v>
+        <v>00:42:59</v>
       </c>
     </row>
     <row r="12">
@@ -596,13 +596,13 @@
         <v>3841</v>
       </c>
       <c r="C12" t="str">
-        <v>2026/07/27 14:39:09</v>
+        <v>2026/07/28 14:35:30</v>
       </c>
       <c r="D12" t="str">
-        <v>2026/07/27 15:56:16</v>
+        <v>2026/07/28 14:49:15</v>
       </c>
       <c r="E12" t="str">
-        <v>01:17:07</v>
+        <v>00:13:45</v>
       </c>
     </row>
     <row r="13">
@@ -613,13 +613,13 @@
         <v>3841</v>
       </c>
       <c r="C13" t="str">
-        <v>2026/07/27 17:30:08</v>
+        <v>2026/07/28 16:39:55</v>
       </c>
       <c r="D13" t="str">
-        <v>2026/07/27 17:31:54</v>
+        <v>2026/07/28 16:41:47</v>
       </c>
       <c r="E13" t="str">
-        <v>00:01:46</v>
+        <v>00:01:52</v>
       </c>
     </row>
     <row r="14">
@@ -630,13 +630,13 @@
         <v>3841</v>
       </c>
       <c r="C14" t="str">
-        <v>2026/07/27 18:32:36</v>
+        <v>2026/07/28 19:54:31</v>
       </c>
       <c r="D14" t="str">
-        <v>2026/07/27 18:35:51</v>
+        <v>2026/07/28 20:24:31</v>
       </c>
       <c r="E14" t="str">
-        <v>00:03:15</v>
+        <v>00:30:00</v>
       </c>
     </row>
     <row r="15">
@@ -647,13 +647,13 @@
         <v>3841</v>
       </c>
       <c r="C15" t="str">
-        <v>2026/07/27 19:32:55</v>
+        <v>2026/07/29 13:28:36</v>
       </c>
       <c r="D15" t="str">
-        <v>2026/07/27 20:22:58</v>
+        <v>2026/07/29 13:55:48</v>
       </c>
       <c r="E15" t="str">
-        <v>00:50:03</v>
+        <v>00:27:12</v>
       </c>
     </row>
     <row r="16">
@@ -664,13 +664,13 @@
         <v>3841</v>
       </c>
       <c r="C16" t="str">
-        <v>2026/07/27 20:45:58</v>
+        <v>2026/07/29 15:08:07</v>
       </c>
       <c r="D16" t="str">
-        <v>2026/07/27 21:10:14</v>
+        <v>2026/07/29 15:15:09</v>
       </c>
       <c r="E16" t="str">
-        <v>00:24:16</v>
+        <v>00:07:02</v>
       </c>
     </row>
     <row r="17">
@@ -681,13 +681,13 @@
         <v>3841</v>
       </c>
       <c r="C17" t="str">
-        <v>2026/07/27 21:50:35</v>
+        <v>2026/07/29 16:42:48</v>
       </c>
       <c r="D17" t="str">
-        <v>2026/07/27 22:08:20</v>
+        <v>2026/07/29 17:12:15</v>
       </c>
       <c r="E17" t="str">
-        <v>00:17:45</v>
+        <v>00:29:27</v>
       </c>
     </row>
     <row r="18">
@@ -698,13 +698,13 @@
         <v>3841</v>
       </c>
       <c r="C18" t="str">
-        <v>2026/07/27 22:23:35</v>
+        <v>2026/07/29 17:39:15</v>
       </c>
       <c r="D18" t="str">
-        <v>2026/07/27 22:36:39</v>
+        <v>2026/07/29 17:45:25</v>
       </c>
       <c r="E18" t="str">
-        <v>00:13:04</v>
+        <v>00:06:10</v>
       </c>
     </row>
     <row r="19">
@@ -715,13 +715,13 @@
         <v>3841</v>
       </c>
       <c r="C19" t="str">
-        <v>2026/07/28 02:34:49</v>
+        <v>2026/07/29 18:53:31</v>
       </c>
       <c r="D19" t="str">
-        <v>2026/07/28 02:44:51</v>
+        <v>2026/07/29 19:58:45</v>
       </c>
       <c r="E19" t="str">
-        <v>00:10:02</v>
+        <v>01:05:14</v>
       </c>
     </row>
     <row r="20">
@@ -732,13 +732,13 @@
         <v>3841</v>
       </c>
       <c r="C20" t="str">
-        <v>2026/07/28 13:21:06</v>
+        <v>2026/07/30 13:01:09</v>
       </c>
       <c r="D20" t="str">
-        <v>2026/07/28 14:04:05</v>
+        <v>2026/07/30 13:08:44</v>
       </c>
       <c r="E20" t="str">
-        <v>00:42:59</v>
+        <v>00:07:35</v>
       </c>
     </row>
     <row r="21">
@@ -749,13 +749,13 @@
         <v>3841</v>
       </c>
       <c r="C21" t="str">
-        <v>2026/07/28 14:35:30</v>
+        <v>2026/07/30 20:16:41</v>
       </c>
       <c r="D21" t="str">
-        <v>2026/07/28 14:49:15</v>
+        <v>2026/07/30 20:51:01</v>
       </c>
       <c r="E21" t="str">
-        <v>00:13:45</v>
+        <v>00:34:20</v>
       </c>
     </row>
     <row r="22">
@@ -766,13 +766,13 @@
         <v>3841</v>
       </c>
       <c r="C22" t="str">
-        <v>2026/07/28 16:39:55</v>
+        <v>2026/07/31 18:04:58</v>
       </c>
       <c r="D22" t="str">
-        <v>2026/07/28 16:41:47</v>
+        <v>2026/07/31 19:59:09</v>
       </c>
       <c r="E22" t="str">
-        <v>00:01:52</v>
+        <v>01:54:11</v>
       </c>
     </row>
     <row r="23">
@@ -783,13 +783,13 @@
         <v>3841</v>
       </c>
       <c r="C23" t="str">
-        <v>2026/07/28 19:54:31</v>
+        <v>2026/08/01 04:47:28</v>
       </c>
       <c r="D23" t="str">
-        <v>2026/07/28 20:24:31</v>
+        <v>2026/08/01 04:54:37</v>
       </c>
       <c r="E23" t="str">
-        <v>00:30:00</v>
+        <v>00:07:09</v>
       </c>
     </row>
     <row r="24">
@@ -800,484 +800,331 @@
         <v>3841</v>
       </c>
       <c r="C24" t="str">
-        <v>2026/07/29 13:28:36</v>
+        <v>2026/08/02 17:18:31</v>
       </c>
       <c r="D24" t="str">
-        <v>2026/07/29 13:55:48</v>
+        <v>2026/08/02 17:19:53</v>
       </c>
       <c r="E24" t="str">
-        <v>00:27:12</v>
+        <v>00:01:22</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>MAXUS SRYB-26 (ANTOFA)</v>
+        <v>MAXUS TVVB-25 (CHILLAN)</v>
       </c>
       <c r="B25">
-        <v>3841</v>
+        <v>4936</v>
       </c>
       <c r="C25" t="str">
-        <v>2026/07/29 15:08:07</v>
+        <v>2026/07/31 21:15:59</v>
       </c>
       <c r="D25" t="str">
-        <v>2026/07/29 15:15:09</v>
+        <v>2026/07/31 22:11:48</v>
       </c>
       <c r="E25" t="str">
-        <v>00:07:02</v>
+        <v>00:55:49</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>MAXUS SRYB-26 (ANTOFA)</v>
+        <v>MAXUS TVVB-25 (CHILLAN)</v>
       </c>
       <c r="B26">
-        <v>3841</v>
+        <v>4936</v>
       </c>
       <c r="C26" t="str">
-        <v>2026/07/29 16:42:48</v>
+        <v>2026/07/31 23:34:38</v>
       </c>
       <c r="D26" t="str">
-        <v>2026/07/29 17:12:15</v>
+        <v>2026/07/31 23:37:30</v>
       </c>
       <c r="E26" t="str">
-        <v>00:29:27</v>
+        <v>00:02:52</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>MAXUS SRYB-26 (ANTOFA)</v>
+        <v>MAXUS TYTC-88 (ANTOFA)</v>
       </c>
       <c r="B27">
-        <v>3841</v>
+        <v>3860</v>
       </c>
       <c r="C27" t="str">
-        <v>2026/07/29 17:39:15</v>
+        <v>2026/07/29 14:19:49</v>
       </c>
       <c r="D27" t="str">
-        <v>2026/07/29 17:45:25</v>
+        <v>2026/07/29 14:20:58</v>
       </c>
       <c r="E27" t="str">
-        <v>00:06:10</v>
+        <v>00:01:09</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>MAXUS SRYB-26 (ANTOFA)</v>
+        <v>MAXUS TYTC-88 (ANTOFA)</v>
       </c>
       <c r="B28">
-        <v>3841</v>
+        <v>3860</v>
       </c>
       <c r="C28" t="str">
-        <v>2026/07/29 18:53:31</v>
+        <v>2026/07/30 19:44:10</v>
       </c>
       <c r="D28" t="str">
-        <v>2026/07/29 19:58:45</v>
+        <v>2026/07/30 19:57:33</v>
       </c>
       <c r="E28" t="str">
-        <v>01:05:14</v>
+        <v>00:13:23</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>MAXUS SRYB-26 (ANTOFA)</v>
+        <v>MAXUS TYTC-88 (ANTOFA)</v>
       </c>
       <c r="B29">
-        <v>3841</v>
+        <v>3860</v>
       </c>
       <c r="C29" t="str">
-        <v>2026/07/30 13:01:09</v>
+        <v>2026/07/30 20:16:18</v>
       </c>
       <c r="D29" t="str">
-        <v>2026/07/30 13:08:44</v>
+        <v>2026/07/30 20:29:00</v>
       </c>
       <c r="E29" t="str">
-        <v>00:07:35</v>
+        <v>00:12:42</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>MAXUS SRYB-26 (ANTOFA)</v>
+        <v>MAXUS TYTC-88 (ANTOFA)</v>
       </c>
       <c r="B30">
-        <v>3841</v>
+        <v>3860</v>
       </c>
       <c r="C30" t="str">
-        <v>2026/07/30 20:16:41</v>
+        <v>2026/07/31 17:47:49</v>
       </c>
       <c r="D30" t="str">
-        <v>2026/07/30 20:51:01</v>
+        <v>2026/07/31 19:42:43</v>
       </c>
       <c r="E30" t="str">
-        <v>00:34:20</v>
+        <v>01:54:54</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>MAXUS SRYB-26 (ANTOFA)</v>
+        <v>MAXUS VGVV-89 (STGO)</v>
       </c>
       <c r="B31">
-        <v>3841</v>
+        <v>5633</v>
       </c>
       <c r="C31" t="str">
-        <v>2026/07/31 18:04:58</v>
+        <v>2026/07/29 13:57:54</v>
       </c>
       <c r="D31" t="str">
-        <v>2026/07/31 19:59:09</v>
+        <v>2026/07/29 16:12:06</v>
       </c>
       <c r="E31" t="str">
-        <v>01:54:11</v>
+        <v>02:14:12</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>MAXUS SRYB-26 (ANTOFA)</v>
+        <v>MAXUS VGVV-89 (STGO)</v>
       </c>
       <c r="B32">
-        <v>3841</v>
+        <v>5633</v>
       </c>
       <c r="C32" t="str">
-        <v>2026/08/01 04:47:28</v>
+        <v>2026/07/30 14:07:47</v>
       </c>
       <c r="D32" t="str">
-        <v>2026/08/01 04:54:37</v>
+        <v>2026/07/30 14:16:07</v>
       </c>
       <c r="E32" t="str">
-        <v>00:07:09</v>
+        <v>00:08:20</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>MAXUS SRYB-26 (ANTOFA)</v>
+        <v>MAXUS VGVV-89 (STGO)</v>
       </c>
       <c r="B33">
-        <v>3841</v>
+        <v>5633</v>
       </c>
       <c r="C33" t="str">
-        <v>2026/08/02 17:18:31</v>
+        <v>2026/07/30 14:26:37</v>
       </c>
       <c r="D33" t="str">
-        <v>2026/08/02 17:19:53</v>
+        <v>2026/07/30 14:38:59</v>
       </c>
       <c r="E33" t="str">
-        <v>00:01:22</v>
+        <v>00:12:22</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>MAXUS TVVB-25 (CHILLAN)</v>
+        <v>MAXUS VGVV-89 (STGO)</v>
       </c>
       <c r="B34">
-        <v>4936</v>
+        <v>5633</v>
       </c>
       <c r="C34" t="str">
-        <v>2026/07/31 21:15:59</v>
+        <v>2026/07/30 14:51:32</v>
       </c>
       <c r="D34" t="str">
-        <v>2026/07/31 22:11:48</v>
+        <v>2026/07/30 15:03:31</v>
       </c>
       <c r="E34" t="str">
-        <v>00:55:49</v>
+        <v>00:11:59</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>MAXUS TVVB-25 (CHILLAN)</v>
+        <v>MAXUS VGVV-89 (STGO)</v>
       </c>
       <c r="B35">
-        <v>4936</v>
+        <v>5633</v>
       </c>
       <c r="C35" t="str">
-        <v>2026/07/31 23:34:38</v>
+        <v>2026/07/30 15:26:05</v>
       </c>
       <c r="D35" t="str">
-        <v>2026/07/31 23:37:30</v>
+        <v>2026/07/30 15:46:27</v>
       </c>
       <c r="E35" t="str">
-        <v>00:02:52</v>
+        <v>00:20:22</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>MAXUS TYTC-88 (ANTOFA)</v>
+        <v>MAXUS VGVV-89 (STGO)</v>
       </c>
       <c r="B36">
-        <v>3860</v>
+        <v>5633</v>
       </c>
       <c r="C36" t="str">
-        <v>2026/07/29 14:19:49</v>
+        <v>2026/07/30 16:47:03</v>
       </c>
       <c r="D36" t="str">
-        <v>2026/07/29 14:20:58</v>
+        <v>2026/07/30 16:48:52</v>
       </c>
       <c r="E36" t="str">
-        <v>00:01:09</v>
+        <v>00:01:49</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>MAXUS TYTC-88 (ANTOFA)</v>
+        <v>MITSUBISHI VDYY-73 (Chillan)</v>
       </c>
       <c r="B37">
-        <v>3860</v>
+        <v>5220</v>
       </c>
       <c r="C37" t="str">
-        <v>2026/07/30 19:44:10</v>
+        <v>2026/07/27 15:46:14</v>
       </c>
       <c r="D37" t="str">
-        <v>2026/07/30 19:57:33</v>
+        <v>2026/07/27 15:50:31</v>
       </c>
       <c r="E37" t="str">
-        <v>00:13:23</v>
+        <v>00:04:17</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>MAXUS TYTC-88 (ANTOFA)</v>
+        <v>MITSUBISHI VDYY-73 (Chillan)</v>
       </c>
       <c r="B38">
-        <v>3860</v>
+        <v>5220</v>
       </c>
       <c r="C38" t="str">
-        <v>2026/07/30 20:16:18</v>
+        <v>2026/07/28 20:58:54</v>
       </c>
       <c r="D38" t="str">
-        <v>2026/07/30 20:29:00</v>
+        <v>2026/07/28 21:16:43</v>
       </c>
       <c r="E38" t="str">
-        <v>00:12:42</v>
+        <v>00:17:49</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>MAXUS TYTC-88 (ANTOFA)</v>
+        <v>MITSUBISHI VDYY-82 (ANTOFA)</v>
       </c>
       <c r="B39">
-        <v>3860</v>
+        <v>5635</v>
       </c>
       <c r="C39" t="str">
-        <v>2026/07/31 17:47:49</v>
+        <v>2026/07/28 06:28:24</v>
       </c>
       <c r="D39" t="str">
-        <v>2026/07/31 19:42:43</v>
+        <v>2026/07/28 06:41:26</v>
       </c>
       <c r="E39" t="str">
-        <v>01:54:54</v>
+        <v>00:13:02</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>MAXUS VGVV-89 (STGO)</v>
+        <v>PEUGEOT SVCH-53 (STGO)</v>
       </c>
       <c r="B40">
-        <v>5633</v>
+        <v>5223</v>
       </c>
       <c r="C40" t="str">
-        <v>2026/07/29 13:57:54</v>
+        <v>2026/07/30 15:03:49</v>
       </c>
       <c r="D40" t="str">
-        <v>2026/07/29 16:12:06</v>
+        <v>2026/07/30 15:09:51</v>
       </c>
       <c r="E40" t="str">
-        <v>02:14:12</v>
+        <v>00:06:02</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>MAXUS VGVV-89 (STGO)</v>
+        <v>PEUGEOT SVCH-53 (STGO)</v>
       </c>
       <c r="B41">
-        <v>5633</v>
+        <v>5223</v>
       </c>
       <c r="C41" t="str">
-        <v>2026/07/30 14:07:47</v>
+        <v>2026/07/30 15:25:24</v>
       </c>
       <c r="D41" t="str">
-        <v>2026/07/30 14:16:07</v>
+        <v>2026/07/30 15:55:12</v>
       </c>
       <c r="E41" t="str">
-        <v>00:08:20</v>
+        <v>00:29:48</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>MAXUS VGVV-89 (STGO)</v>
+        <v>PEUGEOT SVCH-53 (STGO)</v>
       </c>
       <c r="B42">
-        <v>5633</v>
+        <v>5223</v>
       </c>
       <c r="C42" t="str">
-        <v>2026/07/30 14:26:37</v>
+        <v>2026/07/30 19:35:42</v>
       </c>
       <c r="D42" t="str">
-        <v>2026/07/30 14:38:59</v>
+        <v>2026/07/30 19:41:13</v>
       </c>
       <c r="E42" t="str">
-        <v>00:12:22</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="str">
-        <v>MAXUS VGVV-89 (STGO)</v>
-      </c>
-      <c r="B43">
-        <v>5633</v>
-      </c>
-      <c r="C43" t="str">
-        <v>2026/07/30 14:51:32</v>
-      </c>
-      <c r="D43" t="str">
-        <v>2026/07/30 15:03:31</v>
-      </c>
-      <c r="E43" t="str">
-        <v>00:11:59</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="str">
-        <v>MAXUS VGVV-89 (STGO)</v>
-      </c>
-      <c r="B44">
-        <v>5633</v>
-      </c>
-      <c r="C44" t="str">
-        <v>2026/07/30 15:26:05</v>
-      </c>
-      <c r="D44" t="str">
-        <v>2026/07/30 15:46:27</v>
-      </c>
-      <c r="E44" t="str">
-        <v>00:20:22</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="str">
-        <v>MAXUS VGVV-89 (STGO)</v>
-      </c>
-      <c r="B45">
-        <v>5633</v>
-      </c>
-      <c r="C45" t="str">
-        <v>2026/07/30 16:47:03</v>
-      </c>
-      <c r="D45" t="str">
-        <v>2026/07/30 16:48:52</v>
-      </c>
-      <c r="E45" t="str">
-        <v>00:01:49</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="str">
-        <v>MITSUBISHI VDYY-73 (Chillan)</v>
-      </c>
-      <c r="B46">
-        <v>5220</v>
-      </c>
-      <c r="C46" t="str">
-        <v>2026/07/27 15:46:14</v>
-      </c>
-      <c r="D46" t="str">
-        <v>2026/07/27 15:50:31</v>
-      </c>
-      <c r="E46" t="str">
-        <v>00:04:17</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="str">
-        <v>MITSUBISHI VDYY-73 (Chillan)</v>
-      </c>
-      <c r="B47">
-        <v>5220</v>
-      </c>
-      <c r="C47" t="str">
-        <v>2026/07/28 20:58:54</v>
-      </c>
-      <c r="D47" t="str">
-        <v>2026/07/28 21:16:43</v>
-      </c>
-      <c r="E47" t="str">
-        <v>00:17:49</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="str">
-        <v>MITSUBISHI VDYY-82 (ANTOFA)</v>
-      </c>
-      <c r="B48">
-        <v>5635</v>
-      </c>
-      <c r="C48" t="str">
-        <v>2026/07/28 06:28:24</v>
-      </c>
-      <c r="D48" t="str">
-        <v>2026/07/28 06:41:26</v>
-      </c>
-      <c r="E48" t="str">
-        <v>00:13:02</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="str">
-        <v>PEUGEOT SVCH-53 (STGO)</v>
-      </c>
-      <c r="B49">
-        <v>5223</v>
-      </c>
-      <c r="C49" t="str">
-        <v>2026/07/30 15:03:49</v>
-      </c>
-      <c r="D49" t="str">
-        <v>2026/07/30 15:09:51</v>
-      </c>
-      <c r="E49" t="str">
-        <v>00:06:02</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="str">
-        <v>PEUGEOT SVCH-53 (STGO)</v>
-      </c>
-      <c r="B50">
-        <v>5223</v>
-      </c>
-      <c r="C50" t="str">
-        <v>2026/07/30 15:25:24</v>
-      </c>
-      <c r="D50" t="str">
-        <v>2026/07/30 15:55:12</v>
-      </c>
-      <c r="E50" t="str">
-        <v>00:29:48</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="str">
-        <v>PEUGEOT SVCH-53 (STGO)</v>
-      </c>
-      <c r="B51">
-        <v>5223</v>
-      </c>
-      <c r="C51" t="str">
-        <v>2026/07/30 19:35:42</v>
-      </c>
-      <c r="D51" t="str">
-        <v>2026/07/30 19:41:13</v>
-      </c>
-      <c r="E51" t="str">
         <v>00:05:31</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E42"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D18"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1295,77 +1142,77 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>EN_0304 (MA9727 Curepto)</v>
+        <v>MAXUS SRYB-26 (ANTOFA)</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-27</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D2" t="str">
-        <v>00:00:07</v>
+        <v>03:33:02</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>EN_0312 (SQM Antofagasta)</v>
+        <v>MAXUS SRYB-26 (ANTOFA)</v>
       </c>
       <c r="B3" t="str">
         <v>2026-07-28</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D3" t="str">
-        <v>02:49:19</v>
+        <v>01:38:38</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>EN_0356 (SQM Antofagasta)</v>
+        <v>MAXUS SRYB-26 (ANTOFA)</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D4" t="str">
-        <v>14:53:52</v>
+        <v>02:15:05</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>EN_0356 (SQM Antofagasta)</v>
+        <v>MAXUS SRYB-26 (ANTOFA)</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
       <c r="D5" t="str">
-        <v>01:16:23</v>
+        <v>00:41:55</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>EN_0356 (SQM Antofagasta)</v>
+        <v>MAXUS SRYB-26 (ANTOFA)</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" t="str">
-        <v>00:09:01</v>
+        <v>01:54:11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>EN_0356 (SQM Antofagasta)</v>
+        <v>MAXUS SRYB-26 (ANTOFA)</v>
       </c>
       <c r="B7" t="str">
         <v>2026-08-01</v>
@@ -1374,7 +1221,7 @@
         <v>1</v>
       </c>
       <c r="D7" t="str">
-        <v>00:19:41</v>
+        <v>00:07:09</v>
       </c>
     </row>
     <row r="8">
@@ -1382,46 +1229,46 @@
         <v>MAXUS SRYB-26 (ANTOFA)</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-07-27</v>
+        <v>2026-08-02</v>
       </c>
       <c r="C8">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D8" t="str">
-        <v>03:33:02</v>
+        <v>00:01:22</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>MAXUS SRYB-26 (ANTOFA)</v>
+        <v>MAXUS TVVB-25 (CHILLAN)</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-31</v>
       </c>
       <c r="C9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D9" t="str">
-        <v>01:38:38</v>
+        <v>00:58:41</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>MAXUS SRYB-26 (ANTOFA)</v>
+        <v>MAXUS TYTC-88 (ANTOFA)</v>
       </c>
       <c r="B10" t="str">
         <v>2026-07-29</v>
       </c>
       <c r="C10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D10" t="str">
-        <v>02:15:05</v>
+        <v>00:01:09</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>MAXUS SRYB-26 (ANTOFA)</v>
+        <v>MAXUS TYTC-88 (ANTOFA)</v>
       </c>
       <c r="B11" t="str">
         <v>2026-07-30</v>
@@ -1430,12 +1277,12 @@
         <v>2</v>
       </c>
       <c r="D11" t="str">
-        <v>00:41:55</v>
+        <v>00:26:05</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>MAXUS SRYB-26 (ANTOFA)</v>
+        <v>MAXUS TYTC-88 (ANTOFA)</v>
       </c>
       <c r="B12" t="str">
         <v>2026-07-31</v>
@@ -1444,187 +1291,103 @@
         <v>1</v>
       </c>
       <c r="D12" t="str">
-        <v>01:54:11</v>
+        <v>01:54:54</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>MAXUS SRYB-26 (ANTOFA)</v>
+        <v>MAXUS VGVV-89 (STGO)</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-08-01</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13" t="str">
-        <v>00:07:09</v>
+        <v>02:14:12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>MAXUS SRYB-26 (ANTOFA)</v>
+        <v>MAXUS VGVV-89 (STGO)</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-08-02</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D14" t="str">
-        <v>00:01:22</v>
+        <v>00:54:52</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>MAXUS TVVB-25 (CHILLAN)</v>
+        <v>MITSUBISHI VDYY-73 (Chillan)</v>
       </c>
       <c r="B15" t="str">
-        <v>2026-07-31</v>
+        <v>2026-07-27</v>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" t="str">
-        <v>00:58:41</v>
+        <v>00:04:17</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>MAXUS TYTC-88 (ANTOFA)</v>
+        <v>MITSUBISHI VDYY-73 (Chillan)</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-28</v>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="D16" t="str">
-        <v>00:01:09</v>
+        <v>00:17:49</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>MAXUS TYTC-88 (ANTOFA)</v>
+        <v>MITSUBISHI VDYY-82 (ANTOFA)</v>
       </c>
       <c r="B17" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-28</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" t="str">
-        <v>00:26:05</v>
+        <v>00:13:02</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>MAXUS TYTC-88 (ANTOFA)</v>
+        <v>PEUGEOT SVCH-53 (STGO)</v>
       </c>
       <c r="B18" t="str">
-        <v>2026-07-31</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18" t="str">
-        <v>01:54:54</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>MAXUS VGVV-89 (STGO)</v>
-      </c>
-      <c r="B19" t="str">
-        <v>2026-07-29</v>
-      </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19" t="str">
-        <v>02:14:12</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>MAXUS VGVV-89 (STGO)</v>
-      </c>
-      <c r="B20" t="str">
-        <v>2026-07-30</v>
-      </c>
-      <c r="C20">
-        <v>5</v>
-      </c>
-      <c r="D20" t="str">
-        <v>00:54:52</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>MITSUBISHI VDYY-73 (Chillan)</v>
-      </c>
-      <c r="B21" t="str">
-        <v>2026-07-27</v>
-      </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21" t="str">
-        <v>00:04:17</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>MITSUBISHI VDYY-73 (Chillan)</v>
-      </c>
-      <c r="B22" t="str">
-        <v>2026-07-28</v>
-      </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22" t="str">
-        <v>00:17:49</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>MITSUBISHI VDYY-82 (ANTOFA)</v>
-      </c>
-      <c r="B23" t="str">
-        <v>2026-07-28</v>
-      </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-      <c r="D23" t="str">
-        <v>00:13:02</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>PEUGEOT SVCH-53 (STGO)</v>
-      </c>
-      <c r="B24" t="str">
-        <v>2026-07-30</v>
-      </c>
-      <c r="C24">
-        <v>3</v>
-      </c>
-      <c r="D24" t="str">
         <v>00:41:21</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D24"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D18"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1639,117 +1402,84 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>EN_0304 (MA9727 Curepto)</v>
+        <v>MAXUS SRYB-26 (ANTOFA)</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C2" t="str">
-        <v>00:00:07</v>
+        <v>10:11:22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>EN_0312 (SQM Antofagasta)</v>
+        <v>MAXUS TVVB-25 (CHILLAN)</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="str">
-        <v>02:49:19</v>
+        <v>00:58:41</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>EN_0356 (SQM Antofagasta)</v>
+        <v>MAXUS TYTC-88 (ANTOFA)</v>
       </c>
       <c r="B4">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C4" t="str">
-        <v>16:38:57</v>
+        <v>02:22:08</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>MAXUS SRYB-26 (ANTOFA)</v>
+        <v>MAXUS VGVV-89 (STGO)</v>
       </c>
       <c r="B5">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="C5" t="str">
-        <v>10:11:22</v>
+        <v>03:09:04</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>MAXUS TVVB-25 (CHILLAN)</v>
+        <v>MITSUBISHI VDYY-73 (Chillan)</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6" t="str">
-        <v>00:58:41</v>
+        <v>00:22:06</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>MAXUS TYTC-88 (ANTOFA)</v>
+        <v>MITSUBISHI VDYY-82 (ANTOFA)</v>
       </c>
       <c r="B7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C7" t="str">
-        <v>02:22:08</v>
+        <v>00:13:02</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>MAXUS VGVV-89 (STGO)</v>
+        <v>PEUGEOT SVCH-53 (STGO)</v>
       </c>
       <c r="B8">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C8" t="str">
-        <v>03:09:04</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>MITSUBISHI VDYY-73 (Chillan)</v>
-      </c>
-      <c r="B9">
-        <v>2</v>
-      </c>
-      <c r="C9" t="str">
-        <v>00:22:06</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>MITSUBISHI VDYY-82 (ANTOFA)</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10" t="str">
-        <v>00:13:02</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>PEUGEOT SVCH-53 (STGO)</v>
-      </c>
-      <c r="B11">
-        <v>3</v>
-      </c>
-      <c r="C11" t="str">
         <v>00:41:21</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C8"/>
   </ignoredErrors>
 </worksheet>
 </file>